--- a/data/staar-wide-x-subj-x-rating-2016-2021.xlsx
+++ b/data/staar-wide-x-subj-x-rating-2016-2021.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/D/Library/Mobile Documents/com~apple~CloudDocs/R Working Directory/scuc-data-analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/D/Library/Mobile Documents/com~apple~CloudDocs/R Working Directory/scuc-data-analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5188AC4C-C787-9D48-A2AB-96D0D9B1D777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3A4251-1262-F74E-AFC0-001F8AB1AB91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2740" yWindow="1500" windowWidth="27300" windowHeight="15940" xr2:uid="{8E9B387D-0C57-BB4F-89EC-39ED4C16F624}"/>
   </bookViews>
@@ -36,16 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="18">
-  <si>
-    <t>approaches</t>
-  </si>
-  <si>
-    <t>meets</t>
-  </si>
-  <si>
-    <t>masters</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t>all subj</t>
   </si>
@@ -90,13 +81,25 @@
   </si>
   <si>
     <t>year end</t>
+  </si>
+  <si>
+    <t>NOTE:  THESE FIGURES ARE ALL GRADE LEVELS COMBINED</t>
+  </si>
+  <si>
+    <t>approaches and above</t>
+  </si>
+  <si>
+    <t>meets and above</t>
+  </si>
+  <si>
+    <t>masters only</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -121,6 +124,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -130,7 +140,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -138,11 +148,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -172,6 +219,19 @@
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,17 +567,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{453406C3-7D24-3942-98C3-0B723D775965}">
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" style="5" customWidth="1"/>
     <col min="3" max="3" width="7.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.140625" style="3" customWidth="1"/>
     <col min="10" max="10" width="15.28515625" style="4" customWidth="1"/>
     <col min="11" max="11" width="9.28515625" style="4" customWidth="1"/>
@@ -527,30 +586,30 @@
     <col min="20" max="16384" width="10.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" ht="38" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" s="1" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="10" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>8</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="10"/>
@@ -566,10 +625,10 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2">
         <v>0.82</v>
@@ -592,10 +651,10 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2">
         <v>0.53</v>
@@ -629,10 +688,10 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2">
         <v>0.22</v>
@@ -666,10 +725,10 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2">
         <v>0.84</v>
@@ -701,10 +760,10 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2">
         <v>0.57999999999999996</v>
@@ -736,10 +795,10 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2">
         <v>0.27</v>
@@ -771,10 +830,10 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2">
         <v>0.84</v>
@@ -806,10 +865,10 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2">
         <v>0.57999999999999996</v>
@@ -841,10 +900,10 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2">
         <v>0.28000000000000003</v>
@@ -876,10 +935,10 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -901,10 +960,10 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -926,10 +985,10 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -951,10 +1010,10 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C14" s="2">
         <v>0.78</v>
@@ -987,10 +1046,10 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2">
         <v>0.52</v>
@@ -1024,10 +1083,10 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C16" s="2">
         <v>0.23</v>
@@ -1061,10 +1120,10 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2">
         <v>0.8</v>
@@ -1098,10 +1157,10 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2">
         <v>0.53</v>
@@ -1135,10 +1194,10 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2">
         <v>0.25</v>
@@ -1172,10 +1231,10 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="C20" s="2">
         <v>0.81</v>
@@ -1207,10 +1266,10 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2">
         <v>0.54</v>
@@ -1242,10 +1301,10 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C22" s="2">
         <v>0.2</v>
@@ -1317,7 +1376,7 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="1"/>
       <c r="C25" s="2"/>
@@ -1338,6 +1397,19 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
     </row>
+    <row r="26" spans="1:19" ht="26" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="16"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
